--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,7 +497,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Textile</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[{"qty": 50, "pricePerUnit": 14.9}, {"qty": 100, "pricePerUnit": 12.5}, {"qty": 200, "pricePerUnit": 10.2}, {"qty": 500, "pricePerUnit": 7.8}]</t>
+          <t>[{"qty": 50, "pricePerUnit": 14.9}, {"qty": 100, "pricePerUnit": 12.5}, {"qty": 200, "pricePerUnit": 10.2}, {"qty": 500, "pricePerUnit": 7.8}, {"qty": 10, "pricePerUnit": 15}]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1586790170083-2f9ceadc732d?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1521572163474-6864f9cf17ab?auto=format&amp;fit=crop&amp;q=80&amp;w=600", "https://images.unsplash.com/photo-1503342250614-ca440b8ec078?auto=format&amp;fit=crop&amp;q=80&amp;w=600", "https://images.unsplash.com/photo-1596755094514-f87e34085b2c?auto=format&amp;fit=crop&amp;q=80&amp;w=600"], "mockup": "https://images.unsplash.com/photo-1576566588028-4147f3842f27?auto=format&amp;fit=crop&amp;q=80&amp;w=600"}</t>
+          <t>{"main": "https://6a2e9676d2c53535166b442c.imgix.net/alfa/1782063236.png?w=1664&amp;h=928"}</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[{"qty": 20, "pricePerUnit": 38.0}, {"qty": 50, "pricePerUnit": 34.0}, {"qty": 100, "pricePerUnit": 32.0}, {"qty": 300, "pricePerUnit": 27.5}]</t>
+          <t>[{"qty": 20, "pricePerUnit": 38}, {"qty": 50, "pricePerUnit": 34}, {"qty": 100, "pricePerUnit": 32}, {"qty": 300, "pricePerUnit": 27.5}]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[{"qty": 50, "pricePerUnit": 22.0}, {"qty": 100, "pricePerUnit": 18.0}, {"qty": 200, "pricePerUnit": 15.5}, {"qty": 500, "pricePerUnit": 12.8}]</t>
+          <t>[{"qty": 50, "pricePerUnit": 22}, {"qty": 100, "pricePerUnit": 18}, {"qty": 200, "pricePerUnit": 15.5}, {"qty": 500, "pricePerUnit": 12.8}]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -662,12 +662,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tote-bag-organic</t>
+          <t>backpack-corporate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Organic Tote Bag</t>
+          <t>Corporate Backpack</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -677,113 +677,113 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tote Bags</t>
+          <t>Backpacks</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>100% organic cotton canvas tote, 4L capacity, reinforced handles. The go-to sustainable merch for eco-forward brands, NGOs, and green campaigns.</t>
+          <t>25L water-resistant polyester backpack with padded laptop sleeve. Subtle branded patch or embroidered logo. Premium conference and welcome kit item.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.2</v>
+        <v>28</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[{"qty": 100, "pricePerUnit": 5.9}, {"qty": 200, "pricePerUnit": 4.2}, {"qty": 500, "pricePerUnit": 3.4}, {"qty": 1000, "pricePerUnit": 2.6}]</t>
+          <t>[{"qty": 50, "pricePerUnit": 36}, {"qty": 100, "pricePerUnit": 28}, {"qty": 200, "pricePerUnit": 24}]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1584917865442-de89df76afd3?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1622560480605-d83c853bc5c3?auto=format&amp;fit=crop&amp;q=80&amp;w=600", "https://images.unsplash.com/photo-1553062407-98eeb64c6a62?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://images.unsplash.com/photo-1553062407-98eeb64c6a62?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1622560480605-d83c853bc5c3?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>green-eco,neutral-beige,vibrant-campaign</t>
+          <t>corporate-blue,luxury-black</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Screen Print,Heat Transfer</t>
+          <t>Embroidery,Patch</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>backpack-corporate</t>
+          <t>notebook-hardcover</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Corporate Backpack</t>
+          <t>Hardcover Notebook A5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bags</t>
+          <t>Notebooks &amp; Stationery</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Backpacks</t>
+          <t>Notebooks</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25L water-resistant polyester backpack with padded laptop sleeve. Subtle branded patch or embroidered logo. Premium conference and welcome kit item.</t>
+          <t>A5 hardcover notebook, 160 pages, dot-grid or lined. Branded debossing or UV print on cover. A premium staple for any conference or onboarding kit.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>6.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[{"qty": 50, "pricePerUnit": 36.0}, {"qty": 100, "pricePerUnit": 28.0}, {"qty": 200, "pricePerUnit": 24.0}]</t>
+          <t>[{"qty": 50, "pricePerUnit": 9.5}, {"qty": 100, "pricePerUnit": 7.8}, {"qty": 200, "pricePerUnit": 6.5}, {"qty": 500, "pricePerUnit": 5.2}]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1553062407-98eeb64c6a62?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1622560480605-d83c853bc5c3?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://images.unsplash.com/photo-1531346878377-a5be20888e57?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1468421870903-4df1664ac249?auto=format&amp;fit=crop&amp;q=80&amp;w=600", "https://images.unsplash.com/photo-1517842645767-c639042777db?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>corporate-blue,luxury-black</t>
+          <t>neutral-beige,luxury-black,corporate-blue,green-eco</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Embroidery,Patch</t>
+          <t>Deboss,UV Print,Foil Stamp</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>notebook-hardcover</t>
+          <t>pen-metal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hardcover Notebook A5</t>
+          <t>Metal Ballpoint Pen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -793,98 +793,96 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Notebooks</t>
+          <t>Pens</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>A5 hardcover notebook, 160 pages, dot-grid or lined. Branded debossing or UV print on cover. A premium staple for any conference or onboarding kit.</t>
+          <t>Premium aluminium barrel ballpoint pen with laser-engraved logo. Smooth-writing refill. Ideal bulk add-on for any stationery or conference kit.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6.5</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[{"qty": 50, "pricePerUnit": 9.5}, {"qty": 100, "pricePerUnit": 7.8}, {"qty": 200, "pricePerUnit": 6.5}, {"qty": 500, "pricePerUnit": 5.2}]</t>
+          <t>[{"qty": 100, "pricePerUnit": 2.2}, {"qty": 500, "pricePerUnit": 1.6}, {"qty": 1000, "pricePerUnit": 1.25}, {"qty": 5000, "pricePerUnit": 0.9}]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1531346878377-a5be20888e57?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1468421870903-4df1664ac249?auto=format&amp;fit=crop&amp;q=80&amp;w=600", "https://images.unsplash.com/photo-1517842645767-c639042777db?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://images.unsplash.com/photo-1585336261022-680e295ce3fe?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1606107557195-0e29a4b5b4aa?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>neutral-beige,luxury-black,corporate-blue,green-eco</t>
+          <t>luxury-black,corporate-blue,neutral-beige</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Deboss,UV Print,Foil Stamp</t>
+          <t>Laser Engrave</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pen-metal</t>
+          <t>mug-ceramic</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Metal Ballpoint Pen</t>
+          <t>Ceramic Mug 330ml</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Notebooks &amp; Stationery</t>
+          <t>Drinkware</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pens</t>
+          <t>Mugs</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Premium aluminium barrel ballpoint pen with laser-engraved logo. Smooth-writing refill. Ideal bulk add-on for any stationery or conference kit.</t>
+          <t>330ml ceramic mug, dishwasher-safe sublimation print. Full-wrap or one-side logo. Pantone color matching available. Classic welcome kit item.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.25</v>
+        <v>4.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[{"qty": 100, "pricePerUnit": 2.2}, {"qty": 500, "pricePerUnit": 1.6}, {"qty": 1000, "pricePerUnit": 1.25}, {"qty": 5000, "pricePerUnit": 0.9}]</t>
+          <t>[{"qty": 50, "pricePerUnit": 6.5}, {"qty": 100, "pricePerUnit": 5.2}, {"qty": 200, "pricePerUnit": 4.5}, {"qty": 500, "pricePerUnit": 3.6}]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1585336261022-680e295ce3fe?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1606107557195-0e29a4b5b4aa?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://6a2e9676d2c53535166b442c.imgix.net/alfa/photo_2026-06-16_14-50-02.jpg?w=1240&amp;h=1280"}</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>luxury-black,corporate-blue,neutral-beige</t>
+          <t>all</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Laser Engrave</t>
+          <t>Sublimation,Screen Print</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
         <v>5</v>
@@ -894,12 +892,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mug-ceramic</t>
+          <t>bottle-steel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ceramic Mug 330ml</t>
+          <t>Insulated Steel Bottle</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -909,113 +907,113 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mugs</t>
+          <t>Bottles</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>330ml ceramic mug, dishwasher-safe sublimation print. Full-wrap or one-side logo. Pantone color matching available. Classic welcome kit item.</t>
+          <t>500ml double-wall stainless steel bottle, keeps drinks cold 24h/hot 12h. Laser-engraved logo, powder-coated finish. Premium eco-friendly promo item.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[{"qty": 50, "pricePerUnit": 6.5}, {"qty": 100, "pricePerUnit": 5.2}, {"qty": 200, "pricePerUnit": 4.5}, {"qty": 500, "pricePerUnit": 3.6}]</t>
+          <t>[{"qty": 50, "pricePerUnit": 18}, {"qty": 100, "pricePerUnit": 14}, {"qty": 200, "pricePerUnit": 12}, {"qty": 500, "pricePerUnit": 9.5}]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1514228742587-6b1558fcc3d1?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1556909114-44e3e70034e2?auto=format&amp;fit=crop&amp;q=80&amp;w=600", "https://images.unsplash.com/photo-1572119865084-43c285814d63?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://images.unsplash.com/photo-1602143407151-7111542de6e8?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1588466585717-f8041aec7875?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>green-eco,luxury-black,corporate-blue</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sublimation,Screen Print</t>
+          <t>Laser Engrave,Pad Print</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>50</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bottle-steel</t>
+          <t>badge-corporate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Insulated Steel Bottle</t>
+          <t>Corporate Badges</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Drinkware</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bottles</t>
+          <t>Badges</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>500ml double-wall stainless steel bottle, keeps drinks cold 24h/hot 12h. Laser-engraved logo, powder-coated finish. Premium eco-friendly promo item.</t>
+          <t>Custom name badges with clip or lanyard hole. Double-sided print, full color. Available in plastic, metal, or biodegradable materials.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>1.8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[{"qty": 50, "pricePerUnit": 18.0}, {"qty": 100, "pricePerUnit": 14.0}, {"qty": 200, "pricePerUnit": 12.0}, {"qty": 500, "pricePerUnit": 9.5}]</t>
+          <t>[{"qty": 100, "pricePerUnit": 2.8}, {"qty": 500, "pricePerUnit": 2}, {"qty": 1000, "pricePerUnit": 1.8}, {"qty": 5000, "pricePerUnit": 1.2}]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1602143407151-7111542de6e8?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1588466585717-f8041aec7875?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://images.unsplash.com/photo-1598914207931-2856f4bc18ca?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1540575467063-178a50c2df87?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>green-eco,luxury-black,corporate-blue</t>
+          <t>all</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Laser Engrave,Pad Print</t>
+          <t>Digital Print,UV Print</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>badge-corporate</t>
+          <t>lanyard-custom</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Corporate Badges</t>
+          <t>Custom Lanyards</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1025,25 +1023,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Badges</t>
+          <t>Lanyards</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Custom name badges with clip or lanyard hole. Double-sided print, full color. Available in plastic, metal, or biodegradable materials.</t>
+          <t>15mm or 20mm polyester sublimation lanyards. Full-color, edge-to-edge branding. Safety clip and badge reel included. Essential conference item.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[{"qty": 100, "pricePerUnit": 2.8}, {"qty": 500, "pricePerUnit": 2.0}, {"qty": 1000, "pricePerUnit": 1.8}, {"qty": 5000, "pricePerUnit": 1.2}]</t>
+          <t>[{"qty": 100, "pricePerUnit": 2}, {"qty": 500, "pricePerUnit": 1.5}, {"qty": 1000, "pricePerUnit": 1.2}, {"qty": 2000, "pricePerUnit": 0.9}]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1598914207931-2856f4bc18ca?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1540575467063-178a50c2df87?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://images.unsplash.com/photo-1629198688000-71f23e745b6e?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1540575467063-178a50c2df87?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1053,358 +1051,301 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Digital Print,UV Print</t>
+          <t>Sublimation,Screen Print</t>
         </is>
       </c>
       <c r="K11" t="n">
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lanyard-custom</t>
+          <t>flyer-a5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Custom Lanyards</t>
+          <t>A5 Flyers (Full Color)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Printing</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lanyards</t>
+          <t>Leaflets</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>15mm or 20mm polyester sublimation lanyards. Full-color, edge-to-edge branding. Safety clip and badge reel included. Essential conference item.</t>
+          <t>A5 double-sided flyers on 170g/m² silk coated stock. 4+4 full-color offset print. Fast turnaround for events, campaigns, and product launches.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>0.12</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[{"qty": 100, "pricePerUnit": 2.0}, {"qty": 500, "pricePerUnit": 1.5}, {"qty": 1000, "pricePerUnit": 1.2}, {"qty": 2000, "pricePerUnit": 0.9}]</t>
+          <t>[{"qty": 1000, "pricePerUnit": 0.25}, {"qty": 5000, "pricePerUnit": 0.16}, {"qty": 10000, "pricePerUnit": 0.12}, {"qty": 50000, "pricePerUnit": 0.07}]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1629198688000-71f23e745b6e?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1540575467063-178a50c2df87?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://images.unsplash.com/photo-1562564055-71e051d33c19?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1586953208448-b95a79798f07?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>vibrant-campaign,all</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sublimation,Screen Print</t>
+          <t>Offset 4+4,Digital</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>flyer-a5</t>
+          <t>cap-snapback</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A5 Flyers (Full Color)</t>
+          <t>Branded Snapback Cap</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>Apparel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Leaflets</t>
+          <t>Headwear</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A5 double-sided flyers on 170g/m² silk coated stock. 4+4 full-color offset print. Fast turnaround for events, campaigns, and product launches.</t>
+          <t>6-panel unstructured snapback with embroidered logo on front panel and woven label inside. Available in 20+ colorways.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[{"qty": 1000, "pricePerUnit": 0.25}, {"qty": 5000, "pricePerUnit": 0.16}, {"qty": 10000, "pricePerUnit": 0.12}, {"qty": 50000, "pricePerUnit": 0.07}]</t>
+          <t>[{"qty": 50, "pricePerUnit": 14.5}, {"qty": 100, "pricePerUnit": 11}, {"qty": 200, "pricePerUnit": 9.8}, {"qty": 500, "pricePerUnit": 7.5}]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1562564055-71e051d33c19?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1586953208448-b95a79798f07?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://images.unsplash.com/photo-1588850561407-ed78c282e89b?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1534215754734-18e55d13e346?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>vibrant-campaign,all</t>
+          <t>vibrant-campaign,luxury-black,neutral-beige</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Offset 4+4,Digital</t>
+          <t>Embroidery,Patch</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cap-snapback</t>
+          <t>packaging-box</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Branded Snapback Cap</t>
+          <t>Custom Gift Box</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Apparel</t>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Headwear</t>
+          <t>Gift Boxes</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6-panel unstructured snapback with embroidered logo on front panel and woven label inside. Available in 20+ colorways.</t>
+          <t>Premium rigid gift box with magnetic closure. Inside tissue paper, ribbon pull. Full-color offset or UV print. Elevates any welcome or press kit to luxury tier.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[{"qty": 50, "pricePerUnit": 14.5}, {"qty": 100, "pricePerUnit": 11.0}, {"qty": 200, "pricePerUnit": 9.8}, {"qty": 500, "pricePerUnit": 7.5}]</t>
+          <t>[{"qty": 50, "pricePerUnit": 14}, {"qty": 100, "pricePerUnit": 10}, {"qty": 200, "pricePerUnit": 8}, {"qty": 500, "pricePerUnit": 6.5}]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1588850561407-ed78c282e89b?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1534215754734-18e55d13e346?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://images.unsplash.com/photo-1513885535751-8b9238bd345a?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1549465220-1a8b9238cd48?auto=format&amp;fit=crop&amp;q=80&amp;w=600", "https://images.unsplash.com/photo-1558618666-fcd25c85cd64?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>vibrant-campaign,luxury-black,neutral-beige</t>
+          <t>luxury-black,neutral-beige,green-eco</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Embroidery,Patch</t>
+          <t>Offset UV,Foil Stamp,Emboss</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>50</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>packaging-box</t>
+          <t>sticker-pack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Custom Gift Box</t>
+          <t>Die-Cut Sticker Pack</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Printing</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Gift Boxes</t>
+          <t>Stickers</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Premium rigid gift box with magnetic closure. Inside tissue paper, ribbon pull. Full-color offset or UV print. Elevates any welcome or press kit to luxury tier.</t>
+          <t>Vinyl die-cut stickers, custom shapes, weatherproof laminate. Packaged in packs of 10 or loose. Great add-on for any brand kit or event bag.</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>0.35</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[{"qty": 50, "pricePerUnit": 14.0}, {"qty": 100, "pricePerUnit": 10.0}, {"qty": 200, "pricePerUnit": 8.0}, {"qty": 500, "pricePerUnit": 6.5}]</t>
+          <t>[{"qty": 100, "pricePerUnit": 0.95}, {"qty": 500, "pricePerUnit": 0.55}, {"qty": 1000, "pricePerUnit": 0.35}, {"qty": 5000, "pricePerUnit": 0.22}]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1513885535751-8b9238bd345a?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1549465220-1a8b9238cd48?auto=format&amp;fit=crop&amp;q=80&amp;w=600", "https://images.unsplash.com/photo-1558618666-fcd25c85cd64?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://images.unsplash.com/photo-1572635196237-14b3f281503f?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1611532736597-de2d4265fba3?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>luxury-black,neutral-beige,green-eco</t>
+          <t>vibrant-campaign,all</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Offset UV,Foil Stamp,Emboss</t>
+          <t>Digital UV</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sticker-pack</t>
+          <t>powerbank-branded</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Die-Cut Sticker Pack</t>
+          <t>Branded Power Bank 10000mAh</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Printing</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Stickers</t>
+          <t>Tech Accessories</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vinyl die-cut stickers, custom shapes, weatherproof laminate. Packaged in packs of 10 or loose. Great add-on for any brand kit or event bag.</t>
+          <t>10,000mAh slim power bank, USB-A + USB-C output. Laser-engraved or pad-printed logo. Premium conference and VIP welcome kit must-have.</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.35</v>
+        <v>18</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[{"qty": 100, "pricePerUnit": 0.95}, {"qty": 500, "pricePerUnit": 0.55}, {"qty": 1000, "pricePerUnit": 0.35}, {"qty": 5000, "pricePerUnit": 0.22}]</t>
+          <t>[{"qty": 25, "pricePerUnit": 26}, {"qty": 50, "pricePerUnit": 22}, {"qty": 100, "pricePerUnit": 18}, {"qty": 250, "pricePerUnit": 15}]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1572635196237-14b3f281503f?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1611532736597-de2d4265fba3?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://images.unsplash.com/photo-1609091839311-d5365f9ff1c5?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1585771724684-38269d6639fd?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>vibrant-campaign,all</t>
+          <t>corporate-blue,luxury-black</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Digital UV</t>
+          <t>Laser Engrave,Pad Print</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>powerbank-branded</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Branded Power Bank 10000mAh</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Tech Accessories</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>10,000mAh slim power bank, USB-A + USB-C output. Laser-engraved or pad-printed logo. Premium conference and VIP welcome kit must-have.</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>18</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>[{"qty": 25, "pricePerUnit": 26.0}, {"qty": 50, "pricePerUnit": 22.0}, {"qty": 100, "pricePerUnit": 18.0}, {"qty": 250, "pricePerUnit": 15.0}]</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>{"main": "https://images.unsplash.com/photo-1609091839311-d5365f9ff1c5?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1585771724684-38269d6639fd?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>corporate-blue,luxury-black</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Laser Engrave,Pad Print</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>25</v>
-      </c>
-      <c r="L17" t="n">
-        <v>14</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1572635196237-14b3f281503f?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1611532736597-de2d4265fba3?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://6a2e9676d2c53535166b442c.imgix.net/alfa/photo_2026-06-22_16-24-46.jpg?w=1280&amp;h=1036"}</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -984,7 +984,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1598914207931-2856f4bc18ca?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1540575467063-178a50c2df87?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://6a2e9676d2c53535166b442c.imgix.net/alfa/image%20(5).jpg?w=1024&amp;h=1008"}</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1531346878377-a5be20888e57?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1468421870903-4df1664ac249?auto=format&amp;fit=crop&amp;q=80&amp;w=600", "https://images.unsplash.com/photo-1517842645767-c639042777db?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://6a2e9676d2c53535166b442c.imgix.net/alfa/photo_2026-06-22_16-29-23.jpg?w=1280&amp;h=945&amp;ar=1280%3A945"}</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -579,7 +579,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1556821840-3a63f95609a7?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1578768079052-aa76e52ff574?auto=format&amp;fit=crop&amp;q=80&amp;w=600", "https://images.unsplash.com/photo-1611329532992-0d4c1b35ad47?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://6a2e9676d2c53535166b442c.imgix.net/alfa/photo_2026-06-22_16-32-10.jpg?w=883&amp;h=1280"}</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1618354691373-d851c5c3a990?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1605518216938-7c31b7b14ad0?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://6a2e9676d2c53535166b442c.imgix.net/alfa/photo_2026-06-22_16-43-23.jpg?w=1280&amp;h=858"}</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1629198688000-71f23e745b6e?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1540575467063-178a50c2df87?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://6a2e9676d2c53535166b442c.imgix.net/alfa/photo_2025-06-17_12-05-33.jpg?w=1216&amp;h=735"}</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A5 Flyers (Full Color)</t>
+          <t xml:space="preserve">A4-sized presentation folder </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A5 double-sided flyers on 170g/m² silk coated stock. 4+4 full-color offset print. Fast turnaround for events, campaigns, and product launches.</t>
+          <t>Material: Premium 350 gsm paperboard (heavyweight cardstock) providing durability and a rigid, high-quality feel.Finish: Smooth laminated coating for extra protection, durability, and a sleek surface appearance.Construction: Die-cut (die-stamped) layout with precise folding lines and an internal pocket to hold documents securely.</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1562564055-71e051d33c19?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1586953208448-b95a79798f07?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://6a2e9676d2c53535166b442c.imgix.net/alfa/photo_2026-06-22_17-08-47.jpg?w=1280&amp;h=1012"}</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -1326,7 +1326,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1609091839311-d5365f9ff1c5?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1585771724684-38269d6639fd?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://6a2e9676d2c53535166b442c.imgix.net/alfa/photo_2023-11-30_12-23-30.jpg?w=997&amp;h=732&amp;rect=0%2C27%2C997%2C732"}</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>{"main": "https://images.unsplash.com/photo-1513885535751-8b9238bd345a?auto=format&amp;fit=crop&amp;q=80&amp;w=800", "gallery": ["https://images.unsplash.com/photo-1549465220-1a8b9238cd48?auto=format&amp;fit=crop&amp;q=80&amp;w=600", "https://images.unsplash.com/photo-1558618666-fcd25c85cd64?auto=format&amp;fit=crop&amp;q=80&amp;w=600"]}</t>
+          <t>{"main": "https://6a2e9676d2c53535166b442c.imgix.net/alfa/photo_2023-11-28_11-30-06.jpg?h=577&amp;w=646&amp;rect=150%2C0%2C646%2C577"}</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
